--- a/05_交付物/通俗细分版_2026-08-07/05_编程数学数据分析和可视化/05-05_并行计算与性能优化/05-05_并行计算与性能优化_GitHub技能调研.xlsx
+++ b/05_交付物/通俗细分版_2026-08-07/05_编程数学数据分析和可视化/05-05_并行计算与性能优化/05-05_并行计算与性能优化_GitHub技能调研.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="rId4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI技能清单" sheetId="2" r:id="rId5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类统计" sheetId="3" r:id="rId6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源清单" sheetId="4" r:id="rId7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="Re0fb64927e624123"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI技能清单" sheetId="2" r:id="Rc091b7defe0b45c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类统计" sheetId="3" r:id="Rc2805c5f190a4f8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源清单" sheetId="4" r:id="R0bb5e1957d6b4fed"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1284,19 +1284,19 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:hyperlinks>
-    <x:hyperlink ref="U5" r:id="rId1"/>
-    <x:hyperlink ref="V5" r:id="rId3"/>
-    <x:hyperlink ref="U6" r:id="rId2"/>
-    <x:hyperlink ref="V6" r:id="rId4"/>
-    <x:hyperlink ref="U7" r:id="rId5"/>
-    <x:hyperlink ref="V7" r:id="rId8"/>
-    <x:hyperlink ref="U8" r:id="rId7"/>
-    <x:hyperlink ref="V8" r:id="rId9"/>
-    <x:hyperlink ref="U9" r:id="rId6"/>
-    <x:hyperlink ref="V9" r:id="rId10"/>
+    <x:hyperlink ref="U5" r:id="rIdHyperlink1"/>
+    <x:hyperlink ref="V5" r:id="rIdHyperlink2"/>
+    <x:hyperlink ref="U6" r:id="rIdHyperlink3"/>
+    <x:hyperlink ref="V6" r:id="rIdHyperlink4"/>
+    <x:hyperlink ref="U7" r:id="rIdHyperlink5"/>
+    <x:hyperlink ref="V7" r:id="rIdHyperlink6"/>
+    <x:hyperlink ref="U8" r:id="rIdHyperlink7"/>
+    <x:hyperlink ref="V8" r:id="rIdHyperlink8"/>
+    <x:hyperlink ref="U9" r:id="rIdHyperlink9"/>
+    <x:hyperlink ref="V9" r:id="rIdHyperlink10"/>
   </x:hyperlinks>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0dcdae70998f4c02"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1568,11 +1568,11 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:hyperlinks>
-    <x:hyperlink ref="B5" r:id="rId1"/>
-    <x:hyperlink ref="B6" r:id="rId2"/>
+    <x:hyperlink ref="B5" r:id="rIdHyperlink1"/>
+    <x:hyperlink ref="B6" r:id="rIdHyperlink2"/>
   </x:hyperlinks>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7284453d33094762"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/05_交付物/通俗细分版_2026-08-07/05_编程数学数据分析和可视化/05-05_并行计算与性能优化/05-05_并行计算与性能优化_GitHub技能调研.xlsx
+++ b/05_交付物/通俗细分版_2026-08-07/05_编程数学数据分析和可视化/05-05_并行计算与性能优化/05-05_并行计算与性能优化_GitHub技能调研.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="Re0fb64927e624123"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI技能清单" sheetId="2" r:id="Rc091b7defe0b45c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类统计" sheetId="3" r:id="Rc2805c5f190a4f8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源清单" sheetId="4" r:id="R0bb5e1957d6b4fed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R719b288fbcdd4fc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI技能清单" sheetId="2" r:id="R83fb6f322be3475e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类统计" sheetId="3" r:id="Re75cf327f7264021"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源清单" sheetId="4" r:id="Rb9a0575a40cf43cd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1296,7 +1296,7 @@
     <x:hyperlink ref="V9" r:id="rIdHyperlink10"/>
   </x:hyperlinks>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0dcdae70998f4c02"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5a3d3da133946ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1572,7 +1572,7 @@
     <x:hyperlink ref="B6" r:id="rIdHyperlink2"/>
   </x:hyperlinks>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7284453d33094762"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b9aed7666c14264"/>
   </x:tableParts>
 </x:worksheet>
 </file>